--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-17).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-17).xlsx
@@ -938,43 +938,43 @@
     <t>215</t>
   </si>
   <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>R$ 9.297,70</t>
-  </si>
-  <si>
-    <t>97.4</t>
-  </si>
-  <si>
-    <t>63.1</t>
-  </si>
-  <si>
-    <t>5.91</t>
-  </si>
-  <si>
-    <t>19.8</t>
-  </si>
-  <si>
-    <t>7.0</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>38.7%</t>
-  </si>
-  <si>
-    <t>16.7%</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 9.347,25</t>
+  </si>
+  <si>
+    <t>97.8</t>
+  </si>
+  <si>
+    <t>62.9</t>
+  </si>
+  <si>
+    <t>5.94</t>
+  </si>
+  <si>
+    <t>20.2</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>35.4%</t>
+  </si>
+  <si>
+    <t>16.6%</t>
   </si>
   <si>
     <t>1.1%</t>
   </si>
   <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>3.3%</t>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>3.5%</t>
   </si>
   <si>
     <t>1.0%</t>
@@ -983,7 +983,7 @@
     <t>0.1%</t>
   </si>
   <si>
-    <t>6.0%</t>
+    <t>5.9%</t>
   </si>
   <si>
     <t>2.1%</t>
@@ -992,40 +992,40 @@
     <t>5.4%</t>
   </si>
   <si>
-    <t>1797.0</t>
-  </si>
-  <si>
-    <t>1534.0</t>
-  </si>
-  <si>
-    <t>105.0</t>
-  </si>
-  <si>
-    <t>36.0</t>
-  </si>
-  <si>
-    <t>301.0</t>
-  </si>
-  <si>
-    <t>89.0</t>
-  </si>
-  <si>
-    <t>9.0</t>
-  </si>
-  <si>
-    <t>553.0</t>
-  </si>
-  <si>
-    <t>197.0</t>
-  </si>
-  <si>
-    <t>501.0</t>
+    <t>2277.0</t>
+  </si>
+  <si>
+    <t>1931.0</t>
+  </si>
+  <si>
+    <t>128.0</t>
+  </si>
+  <si>
+    <t>39.0</t>
+  </si>
+  <si>
+    <t>407.0</t>
+  </si>
+  <si>
+    <t>113.0</t>
+  </si>
+  <si>
+    <t>13.0</t>
+  </si>
+  <si>
+    <t>684.0</t>
+  </si>
+  <si>
+    <t>241.0</t>
+  </si>
+  <si>
+    <t>630.0</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>42.0</t>
+    <t>61.0</t>
   </si>
   <si>
     <t>1</t>
@@ -3746,7 +3746,9 @@
       <c r="N16" s="6">
         <v>59</v>
       </c>
-      <c r="O16" s="6"/>
+      <c r="O16" s="6">
+        <v>28</v>
+      </c>
       <c r="P16" s="7">
         <v>8.685876271186439</v>
       </c>
@@ -3756,31 +3758,75 @@
       <c r="R16" s="8">
         <v>35.655000000000001</v>
       </c>
-      <c r="S16" s="8"/>
+      <c r="S16" s="8">
+        <v>7</v>
+      </c>
       <c r="T16" s="9">
         <v>0.29999999999999999</v>
       </c>
-      <c r="U16" s="9"/>
-      <c r="V16" s="9"/>
-      <c r="W16" s="9"/>
-      <c r="X16" s="9"/>
-      <c r="Y16" s="9"/>
-      <c r="Z16" s="9"/>
-      <c r="AA16" s="9"/>
-      <c r="AB16" s="9"/>
-      <c r="AC16" s="9"/>
-      <c r="AD16" s="6"/>
-      <c r="AE16" s="6"/>
-      <c r="AF16" s="6"/>
-      <c r="AG16" s="6"/>
-      <c r="AH16" s="6"/>
-      <c r="AI16" s="6"/>
-      <c r="AJ16" s="6"/>
-      <c r="AK16" s="6"/>
-      <c r="AL16" s="6"/>
-      <c r="AM16" s="6"/>
-      <c r="AN16" s="9"/>
-      <c r="AO16" s="6"/>
+      <c r="U16" s="9">
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="V16" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="W16" s="9">
+        <v>0</v>
+      </c>
+      <c r="X16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AD16" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE16" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF16" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP16" s="4">
         <v>58</v>
       </c>
@@ -5488,7 +5534,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>51</v>
@@ -5518,35 +5564,93 @@
         <v>58</v>
       </c>
       <c r="L28" s="4"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="9"/>
-      <c r="AD28" s="6"/>
-      <c r="AE28" s="6"/>
-      <c r="AF28" s="6"/>
-      <c r="AG28" s="6"/>
-      <c r="AH28" s="6"/>
-      <c r="AI28" s="6"/>
-      <c r="AJ28" s="6"/>
-      <c r="AK28" s="6"/>
-      <c r="AL28" s="6"/>
-      <c r="AM28" s="6"/>
-      <c r="AN28" s="9"/>
-      <c r="AO28" s="6"/>
+      <c r="M28" s="5">
+        <v>8416.5300000000007</v>
+      </c>
+      <c r="N28" s="6">
+        <v>84</v>
+      </c>
+      <c r="O28" s="6">
+        <v>51</v>
+      </c>
+      <c r="P28" s="7">
+        <v>2.2400402439024392</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>16.399672549019606</v>
+      </c>
+      <c r="R28" s="8">
+        <v>7.2650333333333332</v>
+      </c>
+      <c r="S28" s="8">
+        <v>7</v>
+      </c>
+      <c r="T28" s="9">
+        <v>0.49019607843137253</v>
+      </c>
+      <c r="U28" s="9">
+        <v>0.19607843137254902</v>
+      </c>
+      <c r="V28" s="9">
+        <v>0</v>
+      </c>
+      <c r="W28" s="9">
+        <v>0.019607843137000001</v>
+      </c>
+      <c r="X28" s="9">
+        <v>0.15686274509803921</v>
+      </c>
+      <c r="Y28" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="9">
+        <v>0.039215686274509803</v>
+      </c>
+      <c r="AD28" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH28" s="6">
+        <v>8</v>
+      </c>
+      <c r="AI28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP28" s="4">
         <v>58</v>
       </c>
@@ -6058,7 +6162,7 @@
         <v>19552</v>
       </c>
       <c r="B32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C32" s="4">
         <v>51</v>
@@ -6088,35 +6192,93 @@
         <v>58</v>
       </c>
       <c r="L32" s="4"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="6"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="8"/>
-      <c r="R32" s="8"/>
-      <c r="S32" s="8"/>
-      <c r="T32" s="9"/>
-      <c r="U32" s="9"/>
-      <c r="V32" s="9"/>
-      <c r="W32" s="9"/>
-      <c r="X32" s="9"/>
-      <c r="Y32" s="9"/>
-      <c r="Z32" s="9"/>
-      <c r="AA32" s="9"/>
-      <c r="AB32" s="9"/>
-      <c r="AC32" s="9"/>
-      <c r="AD32" s="6"/>
-      <c r="AE32" s="6"/>
-      <c r="AF32" s="6"/>
-      <c r="AG32" s="6"/>
-      <c r="AH32" s="6"/>
-      <c r="AI32" s="6"/>
-      <c r="AJ32" s="6"/>
-      <c r="AK32" s="6"/>
-      <c r="AL32" s="6"/>
-      <c r="AM32" s="6"/>
-      <c r="AN32" s="9"/>
-      <c r="AO32" s="6"/>
+      <c r="M32" s="5">
+        <v>19610.200000000001</v>
+      </c>
+      <c r="N32" s="6">
+        <v>183</v>
+      </c>
+      <c r="O32" s="6">
+        <v>149</v>
+      </c>
+      <c r="P32" s="7">
+        <v>2.1306774725274726</v>
+      </c>
+      <c r="Q32" s="8">
+        <v>11.813870469798657</v>
+      </c>
+      <c r="R32" s="8">
+        <v>3.7807604026845638</v>
+      </c>
+      <c r="S32" s="8">
+        <v>6</v>
+      </c>
+      <c r="T32" s="9">
+        <v>0.91946308724832215</v>
+      </c>
+      <c r="U32" s="9">
+        <v>0.060402684563758392</v>
+      </c>
+      <c r="V32" s="9">
+        <v>0</v>
+      </c>
+      <c r="W32" s="9">
+        <v>0</v>
+      </c>
+      <c r="X32" s="9">
+        <v>0.060402684563758392</v>
+      </c>
+      <c r="Y32" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE32" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF32" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="6">
+        <v>9</v>
+      </c>
+      <c r="AI32" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP32" s="4">
         <v>58</v>
       </c>
@@ -6157,7 +6319,7 @@
         <v>19553</v>
       </c>
       <c r="B33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C33" s="4">
         <v>51</v>
@@ -6185,35 +6347,93 @@
         <v>58</v>
       </c>
       <c r="L33" s="4"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="8"/>
-      <c r="S33" s="8"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="9"/>
-      <c r="Y33" s="9"/>
-      <c r="Z33" s="9"/>
-      <c r="AA33" s="9"/>
-      <c r="AB33" s="9"/>
-      <c r="AC33" s="9"/>
-      <c r="AD33" s="6"/>
-      <c r="AE33" s="6"/>
-      <c r="AF33" s="6"/>
-      <c r="AG33" s="6"/>
-      <c r="AH33" s="6"/>
-      <c r="AI33" s="6"/>
-      <c r="AJ33" s="6"/>
-      <c r="AK33" s="6"/>
-      <c r="AL33" s="6"/>
-      <c r="AM33" s="6"/>
-      <c r="AN33" s="9"/>
-      <c r="AO33" s="6"/>
+      <c r="M33" s="5">
+        <v>14252.049999999999</v>
+      </c>
+      <c r="N33" s="6">
+        <v>118</v>
+      </c>
+      <c r="O33" s="6">
+        <v>72</v>
+      </c>
+      <c r="P33" s="7">
+        <v>4.5730228813559322</v>
+      </c>
+      <c r="Q33" s="8">
+        <v>17.744444444444444</v>
+      </c>
+      <c r="R33" s="8">
+        <v>5.9168986111111117</v>
+      </c>
+      <c r="S33" s="8">
+        <v>7</v>
+      </c>
+      <c r="T33" s="9">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="U33" s="9">
+        <v>0.15277777777777779</v>
+      </c>
+      <c r="V33" s="9">
+        <v>0.013888888888888888</v>
+      </c>
+      <c r="W33" s="9">
+        <v>0</v>
+      </c>
+      <c r="X33" s="9">
+        <v>0.013888888888888888</v>
+      </c>
+      <c r="Y33" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE33" s="6">
+        <v>11</v>
+      </c>
+      <c r="AF33" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="AO33" s="6">
+        <v>9</v>
+      </c>
       <c t="s" r="AP33" s="4">
         <v>58</v>
       </c>
@@ -7037,7 +7257,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>51</v>
@@ -7067,35 +7287,93 @@
         <v>58</v>
       </c>
       <c r="L39" s="4"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="8"/>
-      <c r="S39" s="8"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="6"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
-      <c r="AH39" s="6"/>
-      <c r="AI39" s="6"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="6"/>
-      <c r="AL39" s="6"/>
-      <c r="AM39" s="6"/>
-      <c r="AN39" s="9"/>
-      <c r="AO39" s="6"/>
+      <c r="M39" s="5">
+        <v>11867.15</v>
+      </c>
+      <c r="N39" s="6">
+        <v>133</v>
+      </c>
+      <c r="O39" s="6">
+        <v>85</v>
+      </c>
+      <c r="P39" s="7">
+        <v>2.8129921259842519</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>18.991568235294118</v>
+      </c>
+      <c r="R39" s="8">
+        <v>8.6369914634146348</v>
+      </c>
+      <c r="S39" s="8">
+        <v>8</v>
+      </c>
+      <c r="T39" s="9">
+        <v>0.32941176470588235</v>
+      </c>
+      <c r="U39" s="9">
+        <v>0.14117647058823529</v>
+      </c>
+      <c r="V39" s="9">
+        <v>0.011764705882352941</v>
+      </c>
+      <c r="W39" s="9">
+        <v>0</v>
+      </c>
+      <c r="X39" s="9">
+        <v>0.094117647058823528</v>
+      </c>
+      <c r="Y39" s="9">
+        <v>0.011764705882352941</v>
+      </c>
+      <c r="Z39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="9">
+        <v>0.047058823529411764</v>
+      </c>
+      <c r="AB39" s="9">
+        <v>0.011764705882352941</v>
+      </c>
+      <c r="AC39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="6">
+        <v>15</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>12</v>
+      </c>
+      <c r="AF39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="6">
+        <v>8</v>
+      </c>
+      <c r="AI39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP39" s="4">
         <v>58</v>
       </c>
@@ -7450,7 +7728,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7480,35 +7758,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>6897.4300000000003</v>
+      </c>
+      <c r="N42" s="6">
+        <v>79</v>
+      </c>
+      <c r="O42" s="6">
+        <v>49</v>
+      </c>
+      <c r="P42" s="7">
+        <v>6.4069259740259739</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>17.703402040816325</v>
+      </c>
+      <c r="R42" s="8">
+        <v>4.5826395833333331</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.30612244897959184</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.10204081632653061</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0.040816326530612242</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.081632653061224483</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -7549,7 +7885,7 @@
         <v>19580</v>
       </c>
       <c r="B43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C43" s="4">
         <v>51</v>
@@ -7579,35 +7915,93 @@
         <v>58</v>
       </c>
       <c r="L43" s="4"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="6"/>
-      <c r="P43" s="7"/>
-      <c r="Q43" s="8"/>
-      <c r="R43" s="8"/>
-      <c r="S43" s="8"/>
-      <c r="T43" s="9"/>
-      <c r="U43" s="9"/>
-      <c r="V43" s="9"/>
-      <c r="W43" s="9"/>
-      <c r="X43" s="9"/>
-      <c r="Y43" s="9"/>
-      <c r="Z43" s="9"/>
-      <c r="AA43" s="9"/>
-      <c r="AB43" s="9"/>
-      <c r="AC43" s="9"/>
-      <c r="AD43" s="6"/>
-      <c r="AE43" s="6"/>
-      <c r="AF43" s="6"/>
-      <c r="AG43" s="6"/>
-      <c r="AH43" s="6"/>
-      <c r="AI43" s="6"/>
-      <c r="AJ43" s="6"/>
-      <c r="AK43" s="6"/>
-      <c r="AL43" s="6"/>
-      <c r="AM43" s="6"/>
-      <c r="AN43" s="9"/>
-      <c r="AO43" s="6"/>
+      <c r="M43" s="5">
+        <v>11426.860000000001</v>
+      </c>
+      <c r="N43" s="6">
+        <v>97</v>
+      </c>
+      <c r="O43" s="6">
+        <v>75</v>
+      </c>
+      <c r="P43" s="7">
+        <v>6.6395185567010317</v>
+      </c>
+      <c r="Q43" s="8">
+        <v>25.057534246575344</v>
+      </c>
+      <c r="R43" s="8">
+        <v>11.194676388888888</v>
+      </c>
+      <c r="S43" s="8">
+        <v>7</v>
+      </c>
+      <c r="T43" s="9">
+        <v>0.013698630136986301</v>
+      </c>
+      <c r="U43" s="9">
+        <v>0.14666666666666667</v>
+      </c>
+      <c r="V43" s="9">
+        <v>0.053333333333333337</v>
+      </c>
+      <c r="W43" s="9">
+        <v>0</v>
+      </c>
+      <c r="X43" s="9">
+        <v>0.053333333333333337</v>
+      </c>
+      <c r="Y43" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="9">
+        <v>0.013333333333333334</v>
+      </c>
+      <c r="AB43" s="9">
+        <v>0.026666666666666668</v>
+      </c>
+      <c r="AC43" s="9">
+        <v>0.026666666666666668</v>
+      </c>
+      <c r="AD43" s="6">
+        <v>13</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>11</v>
+      </c>
+      <c r="AF43" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL43" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM43" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO43" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP43" s="4">
         <v>58</v>
       </c>
@@ -8584,7 +8978,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>51</v>
@@ -8614,35 +9008,93 @@
         <v>58</v>
       </c>
       <c r="L50" s="4"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="8"/>
-      <c r="S50" s="8"/>
-      <c r="T50" s="9"/>
-      <c r="U50" s="9"/>
-      <c r="V50" s="9"/>
-      <c r="W50" s="9"/>
-      <c r="X50" s="9"/>
-      <c r="Y50" s="9"/>
-      <c r="Z50" s="9"/>
-      <c r="AA50" s="9"/>
-      <c r="AB50" s="9"/>
-      <c r="AC50" s="9"/>
-      <c r="AD50" s="6"/>
-      <c r="AE50" s="6"/>
-      <c r="AF50" s="6"/>
-      <c r="AG50" s="6"/>
-      <c r="AH50" s="6"/>
-      <c r="AI50" s="6"/>
-      <c r="AJ50" s="6"/>
-      <c r="AK50" s="6"/>
-      <c r="AL50" s="6"/>
-      <c r="AM50" s="6"/>
-      <c r="AN50" s="9"/>
-      <c r="AO50" s="6"/>
+      <c r="M50" s="5">
+        <v>8260.7600000000002</v>
+      </c>
+      <c r="N50" s="6">
+        <v>94</v>
+      </c>
+      <c r="O50" s="6">
+        <v>63</v>
+      </c>
+      <c r="P50" s="7">
+        <v>2.9688402173913047</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>15.87063492063492</v>
+      </c>
+      <c r="R50" s="8">
+        <v>5.1470435483870967</v>
+      </c>
+      <c r="S50" s="8">
+        <v>8</v>
+      </c>
+      <c r="T50" s="9">
+        <v>0.46031746031746029</v>
+      </c>
+      <c r="U50" s="9">
+        <v>0.20634920634920634</v>
+      </c>
+      <c r="V50" s="9">
+        <v>0</v>
+      </c>
+      <c r="W50" s="9">
+        <v>0</v>
+      </c>
+      <c r="X50" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="Y50" s="9">
+        <v>0.015873015873015872</v>
+      </c>
+      <c r="Z50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="AB50" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AC50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL50" s="6">
+        <v>7</v>
+      </c>
+      <c r="AM50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP50" s="4">
         <v>58</v>
       </c>
@@ -8939,7 +9391,7 @@
         <v>19607</v>
       </c>
       <c r="B53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C53" s="4">
         <v>51</v>
@@ -8967,35 +9419,93 @@
         <v>58</v>
       </c>
       <c r="L53" s="4"/>
-      <c r="M53" s="5"/>
-      <c r="N53" s="6"/>
-      <c r="O53" s="6"/>
-      <c r="P53" s="7"/>
-      <c r="Q53" s="8"/>
-      <c r="R53" s="8"/>
-      <c r="S53" s="8"/>
-      <c r="T53" s="9"/>
-      <c r="U53" s="9"/>
-      <c r="V53" s="9"/>
-      <c r="W53" s="9"/>
-      <c r="X53" s="9"/>
-      <c r="Y53" s="9"/>
-      <c r="Z53" s="9"/>
-      <c r="AA53" s="9"/>
-      <c r="AB53" s="9"/>
-      <c r="AC53" s="9"/>
-      <c r="AD53" s="6"/>
-      <c r="AE53" s="6"/>
-      <c r="AF53" s="6"/>
-      <c r="AG53" s="6"/>
-      <c r="AH53" s="6"/>
-      <c r="AI53" s="6"/>
-      <c r="AJ53" s="6"/>
-      <c r="AK53" s="6"/>
-      <c r="AL53" s="6"/>
-      <c r="AM53" s="6"/>
-      <c r="AN53" s="9"/>
-      <c r="AO53" s="6"/>
+      <c r="M53" s="5">
+        <v>9177.5</v>
+      </c>
+      <c r="N53" s="6">
+        <v>97</v>
+      </c>
+      <c r="O53" s="6">
+        <v>56</v>
+      </c>
+      <c r="P53" s="7">
+        <v>2.6807021052631579</v>
+      </c>
+      <c r="Q53" s="8">
+        <v>12.675892857142857</v>
+      </c>
+      <c r="R53" s="8">
+        <v>2.9750000000000001</v>
+      </c>
+      <c r="S53" s="8">
+        <v>7</v>
+      </c>
+      <c r="T53" s="9">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="U53" s="9">
+        <v>0</v>
+      </c>
+      <c r="V53" s="9">
+        <v>0</v>
+      </c>
+      <c r="W53" s="9">
+        <v>0</v>
+      </c>
+      <c r="X53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP53" s="4">
         <v>58</v>
       </c>
@@ -9193,7 +9703,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>51</v>
@@ -9223,35 +9733,93 @@
         <v>58</v>
       </c>
       <c r="L55" s="4"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="8"/>
-      <c r="S55" s="8"/>
-      <c r="T55" s="9"/>
-      <c r="U55" s="9"/>
-      <c r="V55" s="9"/>
-      <c r="W55" s="9"/>
-      <c r="X55" s="9"/>
-      <c r="Y55" s="9"/>
-      <c r="Z55" s="9"/>
-      <c r="AA55" s="9"/>
-      <c r="AB55" s="9"/>
-      <c r="AC55" s="9"/>
-      <c r="AD55" s="6"/>
-      <c r="AE55" s="6"/>
-      <c r="AF55" s="6"/>
-      <c r="AG55" s="6"/>
-      <c r="AH55" s="6"/>
-      <c r="AI55" s="6"/>
-      <c r="AJ55" s="6"/>
-      <c r="AK55" s="6"/>
-      <c r="AL55" s="6"/>
-      <c r="AM55" s="6"/>
-      <c r="AN55" s="9"/>
-      <c r="AO55" s="6"/>
+      <c r="M55" s="5">
+        <v>11267.07</v>
+      </c>
+      <c r="N55" s="6">
+        <v>129</v>
+      </c>
+      <c r="O55" s="6">
+        <v>92</v>
+      </c>
+      <c r="P55" s="7">
+        <v>3.3671719696969697</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>20.94891304347826</v>
+      </c>
+      <c r="R55" s="8">
+        <v>10.874818478260869</v>
+      </c>
+      <c r="S55" s="8">
+        <v>7</v>
+      </c>
+      <c r="T55" s="9">
+        <v>0.16304347826086957</v>
+      </c>
+      <c r="U55" s="9">
+        <v>0.021739130434782608</v>
+      </c>
+      <c r="V55" s="9">
+        <v>0</v>
+      </c>
+      <c r="W55" s="9">
+        <v>0</v>
+      </c>
+      <c r="X55" s="9">
+        <v>0.021739130434782608</v>
+      </c>
+      <c r="Y55" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP55" s="4">
         <v>58</v>
       </c>
@@ -9326,7 +9894,9 @@
       <c r="N56" s="6">
         <v>172</v>
       </c>
-      <c r="O56" s="6"/>
+      <c r="O56" s="6">
+        <v>118</v>
+      </c>
       <c r="P56" s="7">
         <v>6.4323473372781068</v>
       </c>
@@ -9336,31 +9906,75 @@
       <c r="R56" s="8">
         <v>5.3634782608695648</v>
       </c>
-      <c r="S56" s="8"/>
+      <c r="S56" s="8">
+        <v>8.5</v>
+      </c>
       <c r="T56" s="9">
         <v>0.23728813559322035</v>
       </c>
-      <c r="U56" s="9"/>
-      <c r="V56" s="9"/>
-      <c r="W56" s="9"/>
-      <c r="X56" s="9"/>
-      <c r="Y56" s="9"/>
-      <c r="Z56" s="9"/>
-      <c r="AA56" s="9"/>
-      <c r="AB56" s="9"/>
-      <c r="AC56" s="9"/>
-      <c r="AD56" s="6"/>
-      <c r="AE56" s="6"/>
-      <c r="AF56" s="6"/>
-      <c r="AG56" s="6"/>
-      <c r="AH56" s="6"/>
-      <c r="AI56" s="6"/>
-      <c r="AJ56" s="6"/>
-      <c r="AK56" s="6"/>
-      <c r="AL56" s="6"/>
-      <c r="AM56" s="6"/>
-      <c r="AN56" s="9"/>
-      <c r="AO56" s="6"/>
+      <c r="U56" s="9">
+        <v>0.22033898305084745</v>
+      </c>
+      <c r="V56" s="9">
+        <v>0.025423728813559324</v>
+      </c>
+      <c r="W56" s="9">
+        <v>0</v>
+      </c>
+      <c r="X56" s="9">
+        <v>0.025423728813559324</v>
+      </c>
+      <c r="Y56" s="9">
+        <v>0.0084745762711864406</v>
+      </c>
+      <c r="Z56" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="9">
+        <v>0.11864406779661017</v>
+      </c>
+      <c r="AB56" s="9">
+        <v>0.042372881355932202</v>
+      </c>
+      <c r="AC56" s="9">
+        <v>0.050847457627118647</v>
+      </c>
+      <c r="AD56" s="6">
+        <v>34</v>
+      </c>
+      <c r="AE56" s="6">
+        <v>26</v>
+      </c>
+      <c r="AF56" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG56" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH56" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI56" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ56" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK56" s="6">
+        <v>14</v>
+      </c>
+      <c r="AL56" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM56" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN56" s="9">
+        <v>0.016949152542372881</v>
+      </c>
+      <c r="AO56" s="6">
+        <v>2</v>
+      </c>
       <c t="s" r="AP56" s="4">
         <v>58</v>
       </c>
@@ -9437,7 +10051,9 @@
       <c r="N57" s="6">
         <v>143</v>
       </c>
-      <c r="O57" s="6"/>
+      <c r="O57" s="6">
+        <v>78</v>
+      </c>
       <c r="P57" s="7">
         <v>6.4905639705882345</v>
       </c>
@@ -9447,31 +10063,75 @@
       <c r="R57" s="8">
         <v>4.1307692307692303</v>
       </c>
-      <c r="S57" s="8"/>
+      <c r="S57" s="8">
+        <v>7</v>
+      </c>
       <c r="T57" s="9">
         <v>0.32051282051282054</v>
       </c>
-      <c r="U57" s="9"/>
-      <c r="V57" s="9"/>
-      <c r="W57" s="9"/>
-      <c r="X57" s="9"/>
-      <c r="Y57" s="9"/>
-      <c r="Z57" s="9"/>
-      <c r="AA57" s="9"/>
-      <c r="AB57" s="9"/>
-      <c r="AC57" s="9"/>
-      <c r="AD57" s="6"/>
-      <c r="AE57" s="6"/>
-      <c r="AF57" s="6"/>
-      <c r="AG57" s="6"/>
-      <c r="AH57" s="6"/>
-      <c r="AI57" s="6"/>
-      <c r="AJ57" s="6"/>
-      <c r="AK57" s="6"/>
-      <c r="AL57" s="6"/>
-      <c r="AM57" s="6"/>
-      <c r="AN57" s="9"/>
-      <c r="AO57" s="6"/>
+      <c r="U57" s="9">
+        <v>0.064102564102564097</v>
+      </c>
+      <c r="V57" s="9">
+        <v>0</v>
+      </c>
+      <c r="W57" s="9">
+        <v>0</v>
+      </c>
+      <c r="X57" s="9">
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="Y57" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AB57" s="9">
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="AC57" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI57" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK57" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL57" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM57" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN57" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO57" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP57" s="4">
         <v>58</v>
       </c>
@@ -11427,7 +12087,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>51</v>
@@ -11455,35 +12115,93 @@
         <v>58</v>
       </c>
       <c r="L71" s="4"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="6"/>
-      <c r="O71" s="6"/>
-      <c r="P71" s="7"/>
-      <c r="Q71" s="8"/>
-      <c r="R71" s="8"/>
-      <c r="S71" s="8"/>
-      <c r="T71" s="9"/>
-      <c r="U71" s="9"/>
-      <c r="V71" s="9"/>
-      <c r="W71" s="9"/>
-      <c r="X71" s="9"/>
-      <c r="Y71" s="9"/>
-      <c r="Z71" s="9"/>
-      <c r="AA71" s="9"/>
-      <c r="AB71" s="9"/>
-      <c r="AC71" s="9"/>
-      <c r="AD71" s="6"/>
-      <c r="AE71" s="6"/>
-      <c r="AF71" s="6"/>
-      <c r="AG71" s="6"/>
-      <c r="AH71" s="6"/>
-      <c r="AI71" s="6"/>
-      <c r="AJ71" s="6"/>
-      <c r="AK71" s="6"/>
-      <c r="AL71" s="6"/>
-      <c r="AM71" s="6"/>
-      <c r="AN71" s="9"/>
-      <c r="AO71" s="6"/>
+      <c r="M71" s="5">
+        <v>11262.91</v>
+      </c>
+      <c r="N71" s="6">
+        <v>130</v>
+      </c>
+      <c r="O71" s="6">
+        <v>73</v>
+      </c>
+      <c r="P71" s="7">
+        <v>3.1278648437499998</v>
+      </c>
+      <c r="Q71" s="8">
+        <v>13.823972602739726</v>
+      </c>
+      <c r="R71" s="8">
+        <v>3.5029411764705882</v>
+      </c>
+      <c r="S71" s="8">
+        <v>8</v>
+      </c>
+      <c r="T71" s="9">
+        <v>0.75342465753424659</v>
+      </c>
+      <c r="U71" s="9">
+        <v>0.26027397260273971</v>
+      </c>
+      <c r="V71" s="9">
+        <v>0</v>
+      </c>
+      <c r="W71" s="9">
+        <v>0</v>
+      </c>
+      <c r="X71" s="9">
+        <v>0.054794520547945202</v>
+      </c>
+      <c r="Y71" s="9">
+        <v>0.041095890410958902</v>
+      </c>
+      <c r="Z71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="9">
+        <v>0.21917808219178081</v>
+      </c>
+      <c r="AB71" s="9">
+        <v>0.013698630136986301</v>
+      </c>
+      <c r="AC71" s="9">
+        <v>0.027397260273972601</v>
+      </c>
+      <c r="AD71" s="6">
+        <v>26</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>19</v>
+      </c>
+      <c r="AF71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI71" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="6">
+        <v>16</v>
+      </c>
+      <c r="AL71" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM71" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP71" s="4">
         <v>58</v>
       </c>
@@ -11931,7 +12649,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>51</v>
@@ -11961,35 +12679,93 @@
         <v>58</v>
       </c>
       <c r="L75" s="4"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="8"/>
-      <c r="R75" s="8"/>
-      <c r="S75" s="8"/>
-      <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
-      <c r="V75" s="9"/>
-      <c r="W75" s="9"/>
-      <c r="X75" s="9"/>
-      <c r="Y75" s="9"/>
-      <c r="Z75" s="9"/>
-      <c r="AA75" s="9"/>
-      <c r="AB75" s="9"/>
-      <c r="AC75" s="9"/>
-      <c r="AD75" s="6"/>
-      <c r="AE75" s="6"/>
-      <c r="AF75" s="6"/>
-      <c r="AG75" s="6"/>
-      <c r="AH75" s="6"/>
-      <c r="AI75" s="6"/>
-      <c r="AJ75" s="6"/>
-      <c r="AK75" s="6"/>
-      <c r="AL75" s="6"/>
-      <c r="AM75" s="6"/>
-      <c r="AN75" s="9"/>
-      <c r="AO75" s="6"/>
+      <c r="M75" s="5">
+        <v>7619.3500000000004</v>
+      </c>
+      <c r="N75" s="6">
+        <v>78</v>
+      </c>
+      <c r="O75" s="6">
+        <v>39</v>
+      </c>
+      <c r="P75" s="7">
+        <v>5.5681628205128204</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>18.998289743589744</v>
+      </c>
+      <c r="R75" s="8">
+        <v>7.2692973684210527</v>
+      </c>
+      <c r="S75" s="8">
+        <v>7</v>
+      </c>
+      <c r="T75" s="9">
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="U75" s="9">
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="V75" s="9">
+        <v>0</v>
+      </c>
+      <c r="W75" s="9">
+        <v>0</v>
+      </c>
+      <c r="X75" s="9">
+        <v>0.05128205128205128</v>
+      </c>
+      <c r="Y75" s="9">
+        <v>0.02564102564102564</v>
+      </c>
+      <c r="Z75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="9">
+        <v>0.02564102564102564</v>
+      </c>
+      <c r="AB75" s="9">
+        <v>0.12820512820512819</v>
+      </c>
+      <c r="AC75" s="9">
+        <v>0.05128205128205128</v>
+      </c>
+      <c r="AD75" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL75" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM75" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP75" s="4">
         <v>58</v>
       </c>
@@ -12030,7 +12806,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12058,35 +12834,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>9877.0400000000009</v>
+      </c>
+      <c r="N76" s="6">
+        <v>109</v>
+      </c>
+      <c r="O76" s="6">
+        <v>52</v>
+      </c>
+      <c r="P76" s="7">
+        <v>7.0663716814159292</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>29.334936538461537</v>
+      </c>
+      <c r="R76" s="8">
+        <v>13.754901960784315</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.057692307692307696</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>12</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -13319,7 +14153,7 @@
         <v>19687</v>
       </c>
       <c r="B85" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C85" s="4">
         <v>51</v>
@@ -13349,35 +14183,93 @@
         <v>58</v>
       </c>
       <c r="L85" s="4"/>
-      <c r="M85" s="5"/>
-      <c r="N85" s="6"/>
-      <c r="O85" s="6"/>
-      <c r="P85" s="7"/>
-      <c r="Q85" s="8"/>
-      <c r="R85" s="8"/>
-      <c r="S85" s="8"/>
-      <c r="T85" s="9"/>
-      <c r="U85" s="9"/>
-      <c r="V85" s="9"/>
-      <c r="W85" s="9"/>
-      <c r="X85" s="9"/>
-      <c r="Y85" s="9"/>
-      <c r="Z85" s="9"/>
-      <c r="AA85" s="9"/>
-      <c r="AB85" s="9"/>
-      <c r="AC85" s="9"/>
-      <c r="AD85" s="6"/>
-      <c r="AE85" s="6"/>
-      <c r="AF85" s="6"/>
-      <c r="AG85" s="6"/>
-      <c r="AH85" s="6"/>
-      <c r="AI85" s="6"/>
-      <c r="AJ85" s="6"/>
-      <c r="AK85" s="6"/>
-      <c r="AL85" s="6"/>
-      <c r="AM85" s="6"/>
-      <c r="AN85" s="9"/>
-      <c r="AO85" s="6"/>
+      <c r="M85" s="5">
+        <v>11344.75</v>
+      </c>
+      <c r="N85" s="6">
+        <v>142</v>
+      </c>
+      <c r="O85" s="6">
+        <v>16</v>
+      </c>
+      <c r="P85" s="7">
+        <v>7.5879940677966102</v>
+      </c>
+      <c r="Q85" s="8">
+        <v>65.696875000000006</v>
+      </c>
+      <c r="R85" s="8">
+        <v>55.169999999999995</v>
+      </c>
+      <c r="S85" s="8">
+        <v>7</v>
+      </c>
+      <c r="T85" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="U85" s="9">
+        <v>0.5625</v>
+      </c>
+      <c r="V85" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="W85" s="9">
+        <v>0</v>
+      </c>
+      <c r="X85" s="9">
+        <v>0.1875</v>
+      </c>
+      <c r="Y85" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="Z85" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="AB85" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="AC85" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE85" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF85" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG85" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI85" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ85" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL85" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM85" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN85" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP85" s="4">
         <v>58</v>
       </c>
@@ -16727,7 +17619,7 @@
         <v>19730</v>
       </c>
       <c r="B109" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C109" s="4">
         <v>51</v>
@@ -16755,35 +17647,93 @@
         <v>58</v>
       </c>
       <c r="L109" s="4"/>
-      <c r="M109" s="5"/>
-      <c r="N109" s="6"/>
-      <c r="O109" s="6"/>
-      <c r="P109" s="7"/>
-      <c r="Q109" s="8"/>
-      <c r="R109" s="8"/>
-      <c r="S109" s="8"/>
-      <c r="T109" s="9"/>
-      <c r="U109" s="9"/>
-      <c r="V109" s="9"/>
-      <c r="W109" s="9"/>
-      <c r="X109" s="9"/>
-      <c r="Y109" s="9"/>
-      <c r="Z109" s="9"/>
-      <c r="AA109" s="9"/>
-      <c r="AB109" s="9"/>
-      <c r="AC109" s="9"/>
-      <c r="AD109" s="6"/>
-      <c r="AE109" s="6"/>
-      <c r="AF109" s="6"/>
-      <c r="AG109" s="6"/>
-      <c r="AH109" s="6"/>
-      <c r="AI109" s="6"/>
-      <c r="AJ109" s="6"/>
-      <c r="AK109" s="6"/>
-      <c r="AL109" s="6"/>
-      <c r="AM109" s="6"/>
-      <c r="AN109" s="9"/>
-      <c r="AO109" s="6"/>
+      <c r="M109" s="5">
+        <v>13953.41</v>
+      </c>
+      <c r="N109" s="6">
+        <v>149</v>
+      </c>
+      <c r="O109" s="6">
+        <v>29</v>
+      </c>
+      <c r="P109" s="7">
+        <v>3.6132677631578942</v>
+      </c>
+      <c r="Q109" s="8">
+        <v>31.491379310344829</v>
+      </c>
+      <c r="R109" s="8">
+        <v>19.647127586206896</v>
+      </c>
+      <c r="S109" s="8">
+        <v>8</v>
+      </c>
+      <c r="T109" s="9">
+        <v>0.10344827586206896</v>
+      </c>
+      <c r="U109" s="9">
+        <v>0.34482758620689657</v>
+      </c>
+      <c r="V109" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="W109" s="9">
+        <v>0</v>
+      </c>
+      <c r="X109" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB109" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="AC109" s="9">
+        <v>0.27586206896551724</v>
+      </c>
+      <c r="AD109" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE109" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF109" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL109" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM109" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO109" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP109" s="4">
         <v>58</v>
       </c>
@@ -17676,33 +18626,79 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
       <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
+      <c r="O116" s="6">
+        <v>55</v>
+      </c>
       <c r="P116" s="7"/>
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
-      <c r="S116" s="8"/>
+      <c r="S116" s="8">
+        <v>7</v>
+      </c>
       <c r="T116" s="9"/>
-      <c r="U116" s="9"/>
-      <c r="V116" s="9"/>
-      <c r="W116" s="9"/>
-      <c r="X116" s="9"/>
-      <c r="Y116" s="9"/>
-      <c r="Z116" s="9"/>
-      <c r="AA116" s="9"/>
-      <c r="AB116" s="9"/>
-      <c r="AC116" s="9"/>
-      <c r="AD116" s="6"/>
-      <c r="AE116" s="6"/>
-      <c r="AF116" s="6"/>
-      <c r="AG116" s="6"/>
-      <c r="AH116" s="6"/>
-      <c r="AI116" s="6"/>
-      <c r="AJ116" s="6"/>
-      <c r="AK116" s="6"/>
-      <c r="AL116" s="6"/>
-      <c r="AM116" s="6"/>
-      <c r="AN116" s="9"/>
-      <c r="AO116" s="6"/>
+      <c r="U116" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="V116" s="9">
+        <v>0.036363636363636362</v>
+      </c>
+      <c r="W116" s="9">
+        <v>0</v>
+      </c>
+      <c r="X116" s="9">
+        <v>0.018181818181818181</v>
+      </c>
+      <c r="Y116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="9">
+        <v>0.12727272727272726</v>
+      </c>
+      <c r="AB116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE116" s="6">
+        <v>11</v>
+      </c>
+      <c r="AF116" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN116" s="9">
+        <v>0.018181818181818181</v>
+      </c>
+      <c r="AO116" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP116" s="4">
         <v>58</v>
       </c>
@@ -20128,7 +21124,9 @@
       <c r="N132" s="6">
         <v>152</v>
       </c>
-      <c r="O132" s="6"/>
+      <c r="O132" s="6">
+        <v>138</v>
+      </c>
       <c r="P132" s="7">
         <v>4.1503311258278153</v>
       </c>
@@ -20138,31 +21136,75 @@
       <c r="R132" s="8">
         <v>8.2825873134328365</v>
       </c>
-      <c r="S132" s="8"/>
+      <c r="S132" s="8">
+        <v>6</v>
+      </c>
       <c r="T132" s="9">
         <v>0.34782608695652173</v>
       </c>
-      <c r="U132" s="9"/>
-      <c r="V132" s="9"/>
-      <c r="W132" s="9"/>
-      <c r="X132" s="9"/>
-      <c r="Y132" s="9"/>
-      <c r="Z132" s="9"/>
-      <c r="AA132" s="9"/>
-      <c r="AB132" s="9"/>
-      <c r="AC132" s="9"/>
-      <c r="AD132" s="6"/>
-      <c r="AE132" s="6"/>
-      <c r="AF132" s="6"/>
-      <c r="AG132" s="6"/>
-      <c r="AH132" s="6"/>
-      <c r="AI132" s="6"/>
-      <c r="AJ132" s="6"/>
-      <c r="AK132" s="6"/>
-      <c r="AL132" s="6"/>
-      <c r="AM132" s="6"/>
-      <c r="AN132" s="9"/>
-      <c r="AO132" s="6"/>
+      <c r="U132" s="9">
+        <v>0.34057971014492755</v>
+      </c>
+      <c r="V132" s="9">
+        <v>0</v>
+      </c>
+      <c r="W132" s="9">
+        <v>0</v>
+      </c>
+      <c r="X132" s="9">
+        <v>0.079710144927536225</v>
+      </c>
+      <c r="Y132" s="9">
+        <v>0.021739130434782608</v>
+      </c>
+      <c r="Z132" s="9">
+        <v>0.007246376811594203</v>
+      </c>
+      <c r="AA132" s="9">
+        <v>0.050724637681159424</v>
+      </c>
+      <c r="AB132" s="9">
+        <v>0.007246376811594203</v>
+      </c>
+      <c r="AC132" s="9">
+        <v>0.27536231884057971</v>
+      </c>
+      <c r="AD132" s="6">
+        <v>61</v>
+      </c>
+      <c r="AE132" s="6">
+        <v>47</v>
+      </c>
+      <c r="AF132" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG132" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH132" s="6">
+        <v>11</v>
+      </c>
+      <c r="AI132" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ132" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK132" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL132" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM132" s="6">
+        <v>38</v>
+      </c>
+      <c r="AN132" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO132" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP132" s="4">
         <v>58</v>
       </c>
@@ -20986,7 +22028,7 @@
         <v>19788</v>
       </c>
       <c r="B138" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C138" s="4">
         <v>51</v>
@@ -21014,35 +22056,93 @@
         <v>58</v>
       </c>
       <c r="L138" s="4"/>
-      <c r="M138" s="5"/>
-      <c r="N138" s="6"/>
-      <c r="O138" s="6"/>
-      <c r="P138" s="7"/>
-      <c r="Q138" s="8"/>
-      <c r="R138" s="8"/>
-      <c r="S138" s="8"/>
-      <c r="T138" s="9"/>
-      <c r="U138" s="9"/>
-      <c r="V138" s="9"/>
-      <c r="W138" s="9"/>
-      <c r="X138" s="9"/>
-      <c r="Y138" s="9"/>
-      <c r="Z138" s="9"/>
-      <c r="AA138" s="9"/>
-      <c r="AB138" s="9"/>
-      <c r="AC138" s="9"/>
-      <c r="AD138" s="6"/>
-      <c r="AE138" s="6"/>
-      <c r="AF138" s="6"/>
-      <c r="AG138" s="6"/>
-      <c r="AH138" s="6"/>
-      <c r="AI138" s="6"/>
-      <c r="AJ138" s="6"/>
-      <c r="AK138" s="6"/>
-      <c r="AL138" s="6"/>
-      <c r="AM138" s="6"/>
-      <c r="AN138" s="9"/>
-      <c r="AO138" s="6"/>
+      <c r="M138" s="5">
+        <v>23095.919999999998</v>
+      </c>
+      <c r="N138" s="6">
+        <v>213</v>
+      </c>
+      <c r="O138" s="6">
+        <v>167</v>
+      </c>
+      <c r="P138" s="7">
+        <v>9.3205256157635468</v>
+      </c>
+      <c r="Q138" s="8">
+        <v>22.91207604790419</v>
+      </c>
+      <c r="R138" s="8">
+        <v>7.3763213414634139</v>
+      </c>
+      <c r="S138" s="8">
+        <v>7</v>
+      </c>
+      <c r="T138" s="9">
+        <v>0.09580838323353294</v>
+      </c>
+      <c r="U138" s="9">
+        <v>0.053892215568862277</v>
+      </c>
+      <c r="V138" s="9">
+        <v>0.0059880239520958087</v>
+      </c>
+      <c r="W138" s="9">
+        <v>0.005988023952</v>
+      </c>
+      <c r="X138" s="9">
+        <v>0.023952095808383235</v>
+      </c>
+      <c r="Y138" s="9">
+        <v>0.017964071856287425</v>
+      </c>
+      <c r="Z138" s="9">
+        <v>0.0059880239520958087</v>
+      </c>
+      <c r="AA138" s="9">
+        <v>0.023952095808383235</v>
+      </c>
+      <c r="AB138" s="9">
+        <v>0.0059880239520958087</v>
+      </c>
+      <c r="AC138" s="9">
+        <v>0.011976047904191617</v>
+      </c>
+      <c r="AD138" s="6">
+        <v>17</v>
+      </c>
+      <c r="AE138" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF138" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG138" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH138" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI138" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ138" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK138" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL138" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM138" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN138" s="9">
+        <v>0.0059880239520958087</v>
+      </c>
+      <c r="AO138" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP138" s="4">
         <v>58</v>
       </c>
@@ -24019,7 +25119,9 @@
       <c r="N159" s="6">
         <v>113</v>
       </c>
-      <c r="O159" s="6"/>
+      <c r="O159" s="6">
+        <v>86</v>
+      </c>
       <c r="P159" s="7">
         <v>8.4095026315789472</v>
       </c>
@@ -24029,31 +25131,75 @@
       <c r="R159" s="8">
         <v>7.2327523255813952</v>
       </c>
-      <c r="S159" s="8"/>
+      <c r="S159" s="8">
+        <v>7</v>
+      </c>
       <c r="T159" s="9">
         <v>0.11627906976744186</v>
       </c>
-      <c r="U159" s="9"/>
-      <c r="V159" s="9"/>
-      <c r="W159" s="9"/>
-      <c r="X159" s="9"/>
-      <c r="Y159" s="9"/>
-      <c r="Z159" s="9"/>
-      <c r="AA159" s="9"/>
-      <c r="AB159" s="9"/>
-      <c r="AC159" s="9"/>
-      <c r="AD159" s="6"/>
-      <c r="AE159" s="6"/>
-      <c r="AF159" s="6"/>
-      <c r="AG159" s="6"/>
-      <c r="AH159" s="6"/>
-      <c r="AI159" s="6"/>
-      <c r="AJ159" s="6"/>
-      <c r="AK159" s="6"/>
-      <c r="AL159" s="6"/>
-      <c r="AM159" s="6"/>
-      <c r="AN159" s="9"/>
-      <c r="AO159" s="6"/>
+      <c r="U159" s="9">
+        <v>0.011627906976744186</v>
+      </c>
+      <c r="V159" s="9">
+        <v>0.011627906976744186</v>
+      </c>
+      <c r="W159" s="9">
+        <v>0</v>
+      </c>
+      <c r="X159" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y159" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z159" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA159" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB159" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC159" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD159" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE159" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF159" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN159" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO159" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP159" s="4">
         <v>58</v>
       </c>
@@ -24126,7 +25272,9 @@
       <c r="N160" s="6">
         <v>64</v>
       </c>
-      <c r="O160" s="6"/>
+      <c r="O160" s="6">
+        <v>57</v>
+      </c>
       <c r="P160" s="7">
         <v>7.2466661538461539</v>
       </c>
@@ -24136,31 +25284,75 @@
       <c r="R160" s="8">
         <v>10.829166071428572</v>
       </c>
-      <c r="S160" s="8"/>
+      <c r="S160" s="8">
+        <v>7</v>
+      </c>
       <c r="T160" s="9">
         <v>0.12280701754385964</v>
       </c>
-      <c r="U160" s="9"/>
-      <c r="V160" s="9"/>
-      <c r="W160" s="9"/>
-      <c r="X160" s="9"/>
-      <c r="Y160" s="9"/>
-      <c r="Z160" s="9"/>
-      <c r="AA160" s="9"/>
-      <c r="AB160" s="9"/>
-      <c r="AC160" s="9"/>
-      <c r="AD160" s="6"/>
-      <c r="AE160" s="6"/>
-      <c r="AF160" s="6"/>
-      <c r="AG160" s="6"/>
-      <c r="AH160" s="6"/>
-      <c r="AI160" s="6"/>
-      <c r="AJ160" s="6"/>
-      <c r="AK160" s="6"/>
-      <c r="AL160" s="6"/>
-      <c r="AM160" s="6"/>
-      <c r="AN160" s="9"/>
-      <c r="AO160" s="6"/>
+      <c r="U160" s="9">
+        <v>0.08771929824561403</v>
+      </c>
+      <c r="V160" s="9">
+        <v>0</v>
+      </c>
+      <c r="W160" s="9">
+        <v>0</v>
+      </c>
+      <c r="X160" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y160" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z160" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA160" s="9">
+        <v>0.017543859649122806</v>
+      </c>
+      <c r="AB160" s="9">
+        <v>0.017543859649122806</v>
+      </c>
+      <c r="AC160" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="AD160" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE160" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF160" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG160" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH160" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI160" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ160" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK160" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL160" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM160" s="6">
+        <v>3</v>
+      </c>
+      <c r="AN160" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO160" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP160" s="4">
         <v>58</v>
       </c>
@@ -24235,7 +25427,9 @@
       <c r="N161" s="6">
         <v>101</v>
       </c>
-      <c r="O161" s="6"/>
+      <c r="O161" s="6">
+        <v>5</v>
+      </c>
       <c r="P161" s="7">
         <v>6.7113549450549446</v>
       </c>
@@ -24245,31 +25439,75 @@
       <c r="R161" s="8">
         <v>6.1433400000000002</v>
       </c>
-      <c r="S161" s="8"/>
+      <c r="S161" s="8">
+        <v>5.2999999999999998</v>
+      </c>
       <c r="T161" s="9">
         <v>0.59999999999999998</v>
       </c>
-      <c r="U161" s="9"/>
-      <c r="V161" s="9"/>
-      <c r="W161" s="9"/>
-      <c r="X161" s="9"/>
-      <c r="Y161" s="9"/>
-      <c r="Z161" s="9"/>
-      <c r="AA161" s="9"/>
-      <c r="AB161" s="9"/>
-      <c r="AC161" s="9"/>
-      <c r="AD161" s="6"/>
-      <c r="AE161" s="6"/>
-      <c r="AF161" s="6"/>
-      <c r="AG161" s="6"/>
-      <c r="AH161" s="6"/>
-      <c r="AI161" s="6"/>
-      <c r="AJ161" s="6"/>
-      <c r="AK161" s="6"/>
-      <c r="AL161" s="6"/>
-      <c r="AM161" s="6"/>
-      <c r="AN161" s="9"/>
-      <c r="AO161" s="6"/>
+      <c r="U161" s="9">
+        <v>0</v>
+      </c>
+      <c r="V161" s="9">
+        <v>0</v>
+      </c>
+      <c r="W161" s="9">
+        <v>0</v>
+      </c>
+      <c r="X161" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y161" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z161" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA161" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB161" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC161" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN161" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO161" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP161" s="4">
         <v>58</v>
       </c>
@@ -24310,7 +25548,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>51</v>
@@ -24340,35 +25578,93 @@
         <v>58</v>
       </c>
       <c r="L162" s="4"/>
-      <c r="M162" s="5"/>
-      <c r="N162" s="6"/>
-      <c r="O162" s="6"/>
-      <c r="P162" s="7"/>
-      <c r="Q162" s="8"/>
-      <c r="R162" s="8"/>
-      <c r="S162" s="8"/>
-      <c r="T162" s="9"/>
-      <c r="U162" s="9"/>
-      <c r="V162" s="9"/>
-      <c r="W162" s="9"/>
-      <c r="X162" s="9"/>
-      <c r="Y162" s="9"/>
-      <c r="Z162" s="9"/>
-      <c r="AA162" s="9"/>
-      <c r="AB162" s="9"/>
-      <c r="AC162" s="9"/>
-      <c r="AD162" s="6"/>
-      <c r="AE162" s="6"/>
-      <c r="AF162" s="6"/>
-      <c r="AG162" s="6"/>
-      <c r="AH162" s="6"/>
-      <c r="AI162" s="6"/>
-      <c r="AJ162" s="6"/>
-      <c r="AK162" s="6"/>
-      <c r="AL162" s="6"/>
-      <c r="AM162" s="6"/>
-      <c r="AN162" s="9"/>
-      <c r="AO162" s="6"/>
+      <c r="M162" s="5">
+        <v>12855.799999999999</v>
+      </c>
+      <c r="N162" s="6">
+        <v>120</v>
+      </c>
+      <c r="O162" s="6">
+        <v>80</v>
+      </c>
+      <c r="P162" s="7">
+        <v>30.798275862068966</v>
+      </c>
+      <c r="Q162" s="8">
+        <v>44.548333749999998</v>
+      </c>
+      <c r="R162" s="8">
+        <v>5.2160256410256416</v>
+      </c>
+      <c r="S162" s="8">
+        <v>8</v>
+      </c>
+      <c r="T162" s="9">
+        <v>0</v>
+      </c>
+      <c r="U162" s="9">
+        <v>0.16250000000000001</v>
+      </c>
+      <c r="V162" s="9">
+        <v>0</v>
+      </c>
+      <c r="W162" s="9">
+        <v>0</v>
+      </c>
+      <c r="X162" s="9">
+        <v>0.012500000000000001</v>
+      </c>
+      <c r="Y162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="9">
+        <v>0.037499999999999999</v>
+      </c>
+      <c r="AB162" s="9">
+        <v>0.012500000000000001</v>
+      </c>
+      <c r="AC162" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AD162" s="6">
+        <v>13</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK162" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM162" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO162" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP162" s="4">
         <v>58</v>
       </c>
@@ -24445,7 +25741,9 @@
       <c r="N163" s="6">
         <v>168</v>
       </c>
-      <c r="O163" s="6"/>
+      <c r="O163" s="6">
+        <v>130</v>
+      </c>
       <c r="P163" s="7">
         <v>3.8588890909090905</v>
       </c>
@@ -24455,31 +25753,75 @@
       <c r="R163" s="8">
         <v>14.332791056910569</v>
       </c>
-      <c r="S163" s="8"/>
+      <c r="S163" s="8">
+        <v>8</v>
+      </c>
       <c r="T163" s="9">
         <v>0.17692307692307693</v>
       </c>
-      <c r="U163" s="9"/>
-      <c r="V163" s="9"/>
-      <c r="W163" s="9"/>
-      <c r="X163" s="9"/>
-      <c r="Y163" s="9"/>
-      <c r="Z163" s="9"/>
-      <c r="AA163" s="9"/>
-      <c r="AB163" s="9"/>
-      <c r="AC163" s="9"/>
-      <c r="AD163" s="6"/>
-      <c r="AE163" s="6"/>
-      <c r="AF163" s="6"/>
-      <c r="AG163" s="6"/>
-      <c r="AH163" s="6"/>
-      <c r="AI163" s="6"/>
-      <c r="AJ163" s="6"/>
-      <c r="AK163" s="6"/>
-      <c r="AL163" s="6"/>
-      <c r="AM163" s="6"/>
-      <c r="AN163" s="9"/>
-      <c r="AO163" s="6"/>
+      <c r="U163" s="9">
+        <v>0.17692307692307693</v>
+      </c>
+      <c r="V163" s="9">
+        <v>0</v>
+      </c>
+      <c r="W163" s="9">
+        <v>0</v>
+      </c>
+      <c r="X163" s="9">
+        <v>0.11538461538461539</v>
+      </c>
+      <c r="Y163" s="9">
+        <v>0.053846153846153849</v>
+      </c>
+      <c r="Z163" s="9">
+        <v>0.0076923076923076927</v>
+      </c>
+      <c r="AA163" s="9">
+        <v>0.053846153846153849</v>
+      </c>
+      <c r="AB163" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AC163" s="9">
+        <v>0.030769230769230771</v>
+      </c>
+      <c r="AD163" s="6">
+        <v>41</v>
+      </c>
+      <c r="AE163" s="6">
+        <v>23</v>
+      </c>
+      <c r="AF163" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG163" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH163" s="6">
+        <v>15</v>
+      </c>
+      <c r="AI163" s="6">
+        <v>7</v>
+      </c>
+      <c r="AJ163" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK163" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL163" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM163" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN163" s="9">
+        <v>0.015384615384615385</v>
+      </c>
+      <c r="AO163" s="6">
+        <v>2</v>
+      </c>
       <c t="s" r="AP163" s="4">
         <v>58</v>
       </c>
@@ -25090,7 +26432,7 @@
         <v>19883</v>
       </c>
       <c r="B168" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C168" s="4">
         <v>51</v>
@@ -25120,35 +26462,93 @@
         <v>58</v>
       </c>
       <c r="L168" s="4"/>
-      <c r="M168" s="5"/>
-      <c r="N168" s="6"/>
-      <c r="O168" s="6"/>
-      <c r="P168" s="7"/>
-      <c r="Q168" s="8"/>
-      <c r="R168" s="8"/>
-      <c r="S168" s="8"/>
-      <c r="T168" s="9"/>
-      <c r="U168" s="9"/>
-      <c r="V168" s="9"/>
-      <c r="W168" s="9"/>
-      <c r="X168" s="9"/>
-      <c r="Y168" s="9"/>
-      <c r="Z168" s="9"/>
-      <c r="AA168" s="9"/>
-      <c r="AB168" s="9"/>
-      <c r="AC168" s="9"/>
-      <c r="AD168" s="6"/>
-      <c r="AE168" s="6"/>
-      <c r="AF168" s="6"/>
-      <c r="AG168" s="6"/>
-      <c r="AH168" s="6"/>
-      <c r="AI168" s="6"/>
-      <c r="AJ168" s="6"/>
-      <c r="AK168" s="6"/>
-      <c r="AL168" s="6"/>
-      <c r="AM168" s="6"/>
-      <c r="AN168" s="9"/>
-      <c r="AO168" s="6"/>
+      <c r="M168" s="5">
+        <v>7858</v>
+      </c>
+      <c r="N168" s="6">
+        <v>83</v>
+      </c>
+      <c r="O168" s="6">
+        <v>57</v>
+      </c>
+      <c r="P168" s="7">
+        <v>3.7335337349397593</v>
+      </c>
+      <c r="Q168" s="8">
+        <v>16.327485964912281</v>
+      </c>
+      <c r="R168" s="8">
+        <v>5.9548490909090912</v>
+      </c>
+      <c r="S168" s="8">
+        <v>7</v>
+      </c>
+      <c r="T168" s="9">
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="U168" s="9">
+        <v>0.15789473684210525</v>
+      </c>
+      <c r="V168" s="9">
+        <v>0.035087719298245612</v>
+      </c>
+      <c r="W168" s="9">
+        <v>0</v>
+      </c>
+      <c r="X168" s="9">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="Y168" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z168" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA168" s="9">
+        <v>0.070175438596491224</v>
+      </c>
+      <c r="AB168" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC168" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD168" s="6">
+        <v>12</v>
+      </c>
+      <c r="AE168" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF168" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG168" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH168" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI168" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ168" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK168" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL168" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM168" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN168" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO168" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP168" s="4">
         <v>58</v>
       </c>
@@ -25189,7 +26589,7 @@
         <v>19884</v>
       </c>
       <c r="B169" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C169" s="4">
         <v>51</v>
@@ -25219,35 +26619,93 @@
         <v>58</v>
       </c>
       <c r="L169" s="4"/>
-      <c r="M169" s="5"/>
-      <c r="N169" s="6"/>
-      <c r="O169" s="6"/>
-      <c r="P169" s="7"/>
-      <c r="Q169" s="8"/>
-      <c r="R169" s="8"/>
-      <c r="S169" s="8"/>
-      <c r="T169" s="9"/>
-      <c r="U169" s="9"/>
-      <c r="V169" s="9"/>
-      <c r="W169" s="9"/>
-      <c r="X169" s="9"/>
-      <c r="Y169" s="9"/>
-      <c r="Z169" s="9"/>
-      <c r="AA169" s="9"/>
-      <c r="AB169" s="9"/>
-      <c r="AC169" s="9"/>
-      <c r="AD169" s="6"/>
-      <c r="AE169" s="6"/>
-      <c r="AF169" s="6"/>
-      <c r="AG169" s="6"/>
-      <c r="AH169" s="6"/>
-      <c r="AI169" s="6"/>
-      <c r="AJ169" s="6"/>
-      <c r="AK169" s="6"/>
-      <c r="AL169" s="6"/>
-      <c r="AM169" s="6"/>
-      <c r="AN169" s="9"/>
-      <c r="AO169" s="6"/>
+      <c r="M169" s="5">
+        <v>5265.6999999999998</v>
+      </c>
+      <c r="N169" s="6">
+        <v>55</v>
+      </c>
+      <c r="O169" s="6">
+        <v>41</v>
+      </c>
+      <c r="P169" s="7">
+        <v>6.7672833333333324</v>
+      </c>
+      <c r="Q169" s="8">
+        <v>21.546667500000002</v>
+      </c>
+      <c r="R169" s="8">
+        <v>7.9487179487179489</v>
+      </c>
+      <c r="S169" s="8">
+        <v>7</v>
+      </c>
+      <c r="T169" s="9">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="U169" s="9">
+        <v>0.073170731707317069</v>
+      </c>
+      <c r="V169" s="9">
+        <v>0</v>
+      </c>
+      <c r="W169" s="9">
+        <v>0</v>
+      </c>
+      <c r="X169" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y169" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z169" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="AA169" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="AB169" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="AC169" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD169" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE169" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF169" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG169" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH169" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI169" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ169" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK169" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL169" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM169" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN169" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO169" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP169" s="4">
         <v>58</v>
       </c>
@@ -26731,7 +28189,9 @@
       <c r="N179" s="6">
         <v>142</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>77</v>
+      </c>
       <c r="P179" s="7">
         <v>4.8276978417266188</v>
       </c>
@@ -26741,31 +28201,75 @@
       <c r="R179" s="8">
         <v>2.2209961038961037</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.70129870129870131</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
@@ -26804,7 +28308,7 @@
         <v>19908</v>
       </c>
       <c r="B180" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C180" s="4">
         <v>51</v>
@@ -26834,35 +28338,93 @@
         <v>58</v>
       </c>
       <c r="L180" s="4"/>
-      <c r="M180" s="5"/>
-      <c r="N180" s="6"/>
-      <c r="O180" s="6"/>
-      <c r="P180" s="7"/>
-      <c r="Q180" s="8"/>
-      <c r="R180" s="8"/>
-      <c r="S180" s="8"/>
-      <c r="T180" s="9"/>
-      <c r="U180" s="9"/>
-      <c r="V180" s="9"/>
-      <c r="W180" s="9"/>
-      <c r="X180" s="9"/>
-      <c r="Y180" s="9"/>
-      <c r="Z180" s="9"/>
-      <c r="AA180" s="9"/>
-      <c r="AB180" s="9"/>
-      <c r="AC180" s="9"/>
-      <c r="AD180" s="6"/>
-      <c r="AE180" s="6"/>
-      <c r="AF180" s="6"/>
-      <c r="AG180" s="6"/>
-      <c r="AH180" s="6"/>
-      <c r="AI180" s="6"/>
-      <c r="AJ180" s="6"/>
-      <c r="AK180" s="6"/>
-      <c r="AL180" s="6"/>
-      <c r="AM180" s="6"/>
-      <c r="AN180" s="9"/>
-      <c r="AO180" s="6"/>
+      <c r="M180" s="5">
+        <v>4681.7700000000004</v>
+      </c>
+      <c r="N180" s="6">
+        <v>50</v>
+      </c>
+      <c r="O180" s="6">
+        <v>19</v>
+      </c>
+      <c r="P180" s="7">
+        <v>8.4113340000000001</v>
+      </c>
+      <c r="Q180" s="8">
+        <v>32.30175263157895</v>
+      </c>
+      <c r="R180" s="8">
+        <v>15.252941176470589</v>
+      </c>
+      <c r="S180" s="8">
+        <v>8</v>
+      </c>
+      <c r="T180" s="9">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="U180" s="9">
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="V180" s="9">
+        <v>0</v>
+      </c>
+      <c r="W180" s="9">
+        <v>0</v>
+      </c>
+      <c r="X180" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y180" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA180" s="9">
+        <v>0.15789473684210525</v>
+      </c>
+      <c r="AB180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC180" s="9">
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="AD180" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE180" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK180" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM180" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO180" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP180" s="4">
         <v>58</v>
       </c>
@@ -26903,7 +28465,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>51</v>
@@ -26933,35 +28495,93 @@
         <v>58</v>
       </c>
       <c r="L181" s="4"/>
-      <c r="M181" s="5"/>
-      <c r="N181" s="6"/>
-      <c r="O181" s="6"/>
-      <c r="P181" s="7"/>
-      <c r="Q181" s="8"/>
-      <c r="R181" s="8"/>
-      <c r="S181" s="8"/>
-      <c r="T181" s="9"/>
-      <c r="U181" s="9"/>
-      <c r="V181" s="9"/>
-      <c r="W181" s="9"/>
-      <c r="X181" s="9"/>
-      <c r="Y181" s="9"/>
-      <c r="Z181" s="9"/>
-      <c r="AA181" s="9"/>
-      <c r="AB181" s="9"/>
-      <c r="AC181" s="9"/>
-      <c r="AD181" s="6"/>
-      <c r="AE181" s="6"/>
-      <c r="AF181" s="6"/>
-      <c r="AG181" s="6"/>
-      <c r="AH181" s="6"/>
-      <c r="AI181" s="6"/>
-      <c r="AJ181" s="6"/>
-      <c r="AK181" s="6"/>
-      <c r="AL181" s="6"/>
-      <c r="AM181" s="6"/>
-      <c r="AN181" s="9"/>
-      <c r="AO181" s="6"/>
+      <c r="M181" s="5">
+        <v>5615.8000000000002</v>
+      </c>
+      <c r="N181" s="6">
+        <v>54</v>
+      </c>
+      <c r="O181" s="6">
+        <v>33</v>
+      </c>
+      <c r="P181" s="7">
+        <v>3.3817907407407408</v>
+      </c>
+      <c r="Q181" s="8">
+        <v>10.373233333333333</v>
+      </c>
+      <c r="R181" s="8">
+        <v>2.6320538461538465</v>
+      </c>
+      <c r="S181" s="8">
+        <v>8</v>
+      </c>
+      <c r="T181" s="9">
+        <v>0.87878787878787878</v>
+      </c>
+      <c r="U181" s="9">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="V181" s="9">
+        <v>0</v>
+      </c>
+      <c r="W181" s="9">
+        <v>0</v>
+      </c>
+      <c r="X181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AB181" s="9">
+        <v>0.030303030303030304</v>
+      </c>
+      <c r="AC181" s="9">
+        <v>0.060606060606060608</v>
+      </c>
+      <c r="AD181" s="6">
+        <v>25</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>23</v>
+      </c>
+      <c r="AF181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK181" s="6">
+        <v>22</v>
+      </c>
+      <c r="AL181" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM181" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO181" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP181" s="4">
         <v>58</v>
       </c>
@@ -27195,7 +28815,9 @@
       <c r="N183" s="6">
         <v>90</v>
       </c>
-      <c r="O183" s="6"/>
+      <c r="O183" s="6">
+        <v>49</v>
+      </c>
       <c r="P183" s="7">
         <v>4.9367816091954024</v>
       </c>
@@ -27205,31 +28827,75 @@
       <c r="R183" s="8">
         <v>3.5385177777777779</v>
       </c>
-      <c r="S183" s="8"/>
+      <c r="S183" s="8">
+        <v>8</v>
+      </c>
       <c r="T183" s="9">
         <v>0.55102040816326525</v>
       </c>
-      <c r="U183" s="9"/>
-      <c r="V183" s="9"/>
-      <c r="W183" s="9"/>
-      <c r="X183" s="9"/>
-      <c r="Y183" s="9"/>
-      <c r="Z183" s="9"/>
-      <c r="AA183" s="9"/>
-      <c r="AB183" s="9"/>
-      <c r="AC183" s="9"/>
-      <c r="AD183" s="6"/>
-      <c r="AE183" s="6"/>
-      <c r="AF183" s="6"/>
-      <c r="AG183" s="6"/>
-      <c r="AH183" s="6"/>
-      <c r="AI183" s="6"/>
-      <c r="AJ183" s="6"/>
-      <c r="AK183" s="6"/>
-      <c r="AL183" s="6"/>
-      <c r="AM183" s="6"/>
-      <c r="AN183" s="9"/>
-      <c r="AO183" s="6"/>
+      <c r="U183" s="9">
+        <v>0.16326530612244897</v>
+      </c>
+      <c r="V183" s="9">
+        <v>0.020408163265306121</v>
+      </c>
+      <c r="W183" s="9">
+        <v>0</v>
+      </c>
+      <c r="X183" s="9">
+        <v>0.020408163265306121</v>
+      </c>
+      <c r="Y183" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA183" s="9">
+        <v>0.12244897959183673</v>
+      </c>
+      <c r="AB183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD183" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE183" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF183" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH183" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK183" s="6">
+        <v>6</v>
+      </c>
+      <c r="AL183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO183" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP183" s="4">
         <v>58</v>
       </c>
@@ -27369,7 +29035,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>51</v>
@@ -27625,7 +29291,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>51</v>
@@ -27655,35 +29321,93 @@
         <v>58</v>
       </c>
       <c r="L187" s="4"/>
-      <c r="M187" s="5"/>
-      <c r="N187" s="6"/>
-      <c r="O187" s="6"/>
-      <c r="P187" s="7"/>
-      <c r="Q187" s="8"/>
-      <c r="R187" s="8"/>
-      <c r="S187" s="8"/>
-      <c r="T187" s="9"/>
-      <c r="U187" s="9"/>
-      <c r="V187" s="9"/>
-      <c r="W187" s="9"/>
-      <c r="X187" s="9"/>
-      <c r="Y187" s="9"/>
-      <c r="Z187" s="9"/>
-      <c r="AA187" s="9"/>
-      <c r="AB187" s="9"/>
-      <c r="AC187" s="9"/>
-      <c r="AD187" s="6"/>
-      <c r="AE187" s="6"/>
-      <c r="AF187" s="6"/>
-      <c r="AG187" s="6"/>
-      <c r="AH187" s="6"/>
-      <c r="AI187" s="6"/>
-      <c r="AJ187" s="6"/>
-      <c r="AK187" s="6"/>
-      <c r="AL187" s="6"/>
-      <c r="AM187" s="6"/>
-      <c r="AN187" s="9"/>
-      <c r="AO187" s="6"/>
+      <c r="M187" s="5">
+        <v>2523.5999999999999</v>
+      </c>
+      <c r="N187" s="6">
+        <v>31</v>
+      </c>
+      <c r="O187" s="6">
+        <v>23</v>
+      </c>
+      <c r="P187" s="7">
+        <v>3.7010741935483873</v>
+      </c>
+      <c r="Q187" s="8">
+        <v>13.755073913043477</v>
+      </c>
+      <c r="R187" s="8">
+        <v>3.5355086956521737</v>
+      </c>
+      <c r="S187" s="8">
+        <v>7</v>
+      </c>
+      <c r="T187" s="9">
+        <v>0.69565217391304346</v>
+      </c>
+      <c r="U187" s="9">
+        <v>0.086956521739130432</v>
+      </c>
+      <c r="V187" s="9">
+        <v>0</v>
+      </c>
+      <c r="W187" s="9">
+        <v>0</v>
+      </c>
+      <c r="X187" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="Y187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="AB187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD187" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO187" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP187" s="4">
         <v>58</v>
       </c>
@@ -27881,7 +29605,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>51</v>
@@ -27911,35 +29635,93 @@
         <v>58</v>
       </c>
       <c r="L189" s="4"/>
-      <c r="M189" s="5"/>
-      <c r="N189" s="6"/>
-      <c r="O189" s="6"/>
-      <c r="P189" s="7"/>
-      <c r="Q189" s="8"/>
-      <c r="R189" s="8"/>
-      <c r="S189" s="8"/>
-      <c r="T189" s="9"/>
-      <c r="U189" s="9"/>
-      <c r="V189" s="9"/>
-      <c r="W189" s="9"/>
-      <c r="X189" s="9"/>
-      <c r="Y189" s="9"/>
-      <c r="Z189" s="9"/>
-      <c r="AA189" s="9"/>
-      <c r="AB189" s="9"/>
-      <c r="AC189" s="9"/>
-      <c r="AD189" s="6"/>
-      <c r="AE189" s="6"/>
-      <c r="AF189" s="6"/>
-      <c r="AG189" s="6"/>
-      <c r="AH189" s="6"/>
-      <c r="AI189" s="6"/>
-      <c r="AJ189" s="6"/>
-      <c r="AK189" s="6"/>
-      <c r="AL189" s="6"/>
-      <c r="AM189" s="6"/>
-      <c r="AN189" s="9"/>
-      <c r="AO189" s="6"/>
+      <c r="M189" s="5">
+        <v>6505.96</v>
+      </c>
+      <c r="N189" s="6">
+        <v>83</v>
+      </c>
+      <c r="O189" s="6">
+        <v>73</v>
+      </c>
+      <c r="P189" s="7">
+        <v>6.8172686746987949</v>
+      </c>
+      <c r="Q189" s="8">
+        <v>25.090867123287669</v>
+      </c>
+      <c r="R189" s="8">
+        <v>12.039285714285715</v>
+      </c>
+      <c r="S189" s="8">
+        <v>7</v>
+      </c>
+      <c r="T189" s="9">
+        <v>0.082191780821917804</v>
+      </c>
+      <c r="U189" s="9">
+        <v>0.47945205479452052</v>
+      </c>
+      <c r="V189" s="9">
+        <v>0</v>
+      </c>
+      <c r="W189" s="9">
+        <v>0</v>
+      </c>
+      <c r="X189" s="9">
+        <v>0.041095890410958902</v>
+      </c>
+      <c r="Y189" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA189" s="9">
+        <v>0.068493150684931503</v>
+      </c>
+      <c r="AB189" s="9">
+        <v>0.027397260273972601</v>
+      </c>
+      <c r="AC189" s="9">
+        <v>0.41095890410958902</v>
+      </c>
+      <c r="AD189" s="6">
+        <v>40</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>35</v>
+      </c>
+      <c r="AF189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH189" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK189" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL189" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM189" s="6">
+        <v>30</v>
+      </c>
+      <c r="AN189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO189" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP189" s="4">
         <v>58</v>
       </c>
@@ -27980,7 +29762,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>51</v>
@@ -28010,35 +29792,93 @@
         <v>58</v>
       </c>
       <c r="L190" s="4"/>
-      <c r="M190" s="5"/>
-      <c r="N190" s="6"/>
-      <c r="O190" s="6"/>
-      <c r="P190" s="7"/>
-      <c r="Q190" s="8"/>
-      <c r="R190" s="8"/>
-      <c r="S190" s="8"/>
-      <c r="T190" s="9"/>
-      <c r="U190" s="9"/>
-      <c r="V190" s="9"/>
-      <c r="W190" s="9"/>
-      <c r="X190" s="9"/>
-      <c r="Y190" s="9"/>
-      <c r="Z190" s="9"/>
-      <c r="AA190" s="9"/>
-      <c r="AB190" s="9"/>
-      <c r="AC190" s="9"/>
-      <c r="AD190" s="6"/>
-      <c r="AE190" s="6"/>
-      <c r="AF190" s="6"/>
-      <c r="AG190" s="6"/>
-      <c r="AH190" s="6"/>
-      <c r="AI190" s="6"/>
-      <c r="AJ190" s="6"/>
-      <c r="AK190" s="6"/>
-      <c r="AL190" s="6"/>
-      <c r="AM190" s="6"/>
-      <c r="AN190" s="9"/>
-      <c r="AO190" s="6"/>
+      <c r="M190" s="5">
+        <v>8016.6300000000001</v>
+      </c>
+      <c r="N190" s="6">
+        <v>81</v>
+      </c>
+      <c r="O190" s="6">
+        <v>40</v>
+      </c>
+      <c r="P190" s="7">
+        <v>4.5415641975308638</v>
+      </c>
+      <c r="Q190" s="8">
+        <v>16.292917499999998</v>
+      </c>
+      <c r="R190" s="8">
+        <v>5.192735897435897</v>
+      </c>
+      <c r="S190" s="8">
+        <v>7</v>
+      </c>
+      <c r="T190" s="9">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="U190" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="V190" s="9">
+        <v>0</v>
+      </c>
+      <c r="W190" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="X190" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Y190" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="Z190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="AB190" s="9">
+        <v>0.074999999999999997</v>
+      </c>
+      <c r="AC190" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AD190" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH190" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL190" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM190" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO190" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP190" s="4">
         <v>58</v>
       </c>
@@ -29019,7 +30859,7 @@
         <v>19947</v>
       </c>
       <c r="B197" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C197" s="4">
         <v>51</v>
@@ -29049,35 +30889,93 @@
         <v>58</v>
       </c>
       <c r="L197" s="4"/>
-      <c r="M197" s="5"/>
-      <c r="N197" s="6"/>
-      <c r="O197" s="6"/>
-      <c r="P197" s="7"/>
-      <c r="Q197" s="8"/>
-      <c r="R197" s="8"/>
-      <c r="S197" s="8"/>
-      <c r="T197" s="9"/>
-      <c r="U197" s="9"/>
-      <c r="V197" s="9"/>
-      <c r="W197" s="9"/>
-      <c r="X197" s="9"/>
-      <c r="Y197" s="9"/>
-      <c r="Z197" s="9"/>
-      <c r="AA197" s="9"/>
-      <c r="AB197" s="9"/>
-      <c r="AC197" s="9"/>
-      <c r="AD197" s="6"/>
-      <c r="AE197" s="6"/>
-      <c r="AF197" s="6"/>
-      <c r="AG197" s="6"/>
-      <c r="AH197" s="6"/>
-      <c r="AI197" s="6"/>
-      <c r="AJ197" s="6"/>
-      <c r="AK197" s="6"/>
-      <c r="AL197" s="6"/>
-      <c r="AM197" s="6"/>
-      <c r="AN197" s="9"/>
-      <c r="AO197" s="6"/>
+      <c r="M197" s="5">
+        <v>12560.6</v>
+      </c>
+      <c r="N197" s="6">
+        <v>121</v>
+      </c>
+      <c r="O197" s="6">
+        <v>76</v>
+      </c>
+      <c r="P197" s="7">
+        <v>2.2957627118644064</v>
+      </c>
+      <c r="Q197" s="8">
+        <v>14.091885526315791</v>
+      </c>
+      <c r="R197" s="8">
+        <v>5.126577027027027</v>
+      </c>
+      <c r="S197" s="8">
+        <v>7</v>
+      </c>
+      <c r="T197" s="9">
+        <v>0.57894736842105265</v>
+      </c>
+      <c r="U197" s="9">
+        <v>0.15789473684210525</v>
+      </c>
+      <c r="V197" s="9">
+        <v>0.013157894736842105</v>
+      </c>
+      <c r="W197" s="9">
+        <v>0</v>
+      </c>
+      <c r="X197" s="9">
+        <v>0.092105263157894732</v>
+      </c>
+      <c r="Y197" s="9">
+        <v>0.013157894736842105</v>
+      </c>
+      <c r="Z197" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA197" s="9">
+        <v>0.026315789473684209</v>
+      </c>
+      <c r="AB197" s="9">
+        <v>0.026315789473684209</v>
+      </c>
+      <c r="AC197" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD197" s="6">
+        <v>13</v>
+      </c>
+      <c r="AE197" s="6">
+        <v>12</v>
+      </c>
+      <c r="AF197" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG197" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH197" s="6">
+        <v>7</v>
+      </c>
+      <c r="AI197" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ197" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK197" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL197" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM197" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN197" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO197" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP197" s="4">
         <v>58</v>
       </c>
@@ -29154,7 +31052,9 @@
       <c r="N198" s="6">
         <v>38</v>
       </c>
-      <c r="O198" s="6"/>
+      <c r="O198" s="6">
+        <v>16</v>
+      </c>
       <c r="P198" s="7">
         <v>7.9719289473684203</v>
       </c>
@@ -29164,31 +31064,75 @@
       <c r="R198" s="8">
         <v>3.8218749999999999</v>
       </c>
-      <c r="S198" s="8"/>
+      <c r="S198" s="8">
+        <v>7</v>
+      </c>
       <c r="T198" s="9">
         <v>0.125</v>
       </c>
-      <c r="U198" s="9"/>
-      <c r="V198" s="9"/>
-      <c r="W198" s="9"/>
-      <c r="X198" s="9"/>
-      <c r="Y198" s="9"/>
-      <c r="Z198" s="9"/>
-      <c r="AA198" s="9"/>
-      <c r="AB198" s="9"/>
-      <c r="AC198" s="9"/>
-      <c r="AD198" s="6"/>
-      <c r="AE198" s="6"/>
-      <c r="AF198" s="6"/>
-      <c r="AG198" s="6"/>
-      <c r="AH198" s="6"/>
-      <c r="AI198" s="6"/>
-      <c r="AJ198" s="6"/>
-      <c r="AK198" s="6"/>
-      <c r="AL198" s="6"/>
-      <c r="AM198" s="6"/>
-      <c r="AN198" s="9"/>
-      <c r="AO198" s="6"/>
+      <c r="U198" s="9">
+        <v>0.1875</v>
+      </c>
+      <c r="V198" s="9">
+        <v>0</v>
+      </c>
+      <c r="W198" s="9">
+        <v>0</v>
+      </c>
+      <c r="X198" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y198" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z198" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA198" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB198" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="AC198" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="AD198" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE198" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF198" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG198" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH198" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI198" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ198" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK198" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL198" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM198" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN198" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO198" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP198" s="4">
         <v>58</v>
       </c>
@@ -29229,7 +31173,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>51</v>
@@ -29259,35 +31203,93 @@
         <v>58</v>
       </c>
       <c r="L199" s="4"/>
-      <c r="M199" s="5"/>
-      <c r="N199" s="6"/>
-      <c r="O199" s="6"/>
-      <c r="P199" s="7"/>
-      <c r="Q199" s="8"/>
-      <c r="R199" s="8"/>
-      <c r="S199" s="8"/>
-      <c r="T199" s="9"/>
-      <c r="U199" s="9"/>
-      <c r="V199" s="9"/>
-      <c r="W199" s="9"/>
-      <c r="X199" s="9"/>
-      <c r="Y199" s="9"/>
-      <c r="Z199" s="9"/>
-      <c r="AA199" s="9"/>
-      <c r="AB199" s="9"/>
-      <c r="AC199" s="9"/>
-      <c r="AD199" s="6"/>
-      <c r="AE199" s="6"/>
-      <c r="AF199" s="6"/>
-      <c r="AG199" s="6"/>
-      <c r="AH199" s="6"/>
-      <c r="AI199" s="6"/>
-      <c r="AJ199" s="6"/>
-      <c r="AK199" s="6"/>
-      <c r="AL199" s="6"/>
-      <c r="AM199" s="6"/>
-      <c r="AN199" s="9"/>
-      <c r="AO199" s="6"/>
+      <c r="M199" s="5">
+        <v>6033.8800000000001</v>
+      </c>
+      <c r="N199" s="6">
+        <v>69</v>
+      </c>
+      <c r="O199" s="6">
+        <v>40</v>
+      </c>
+      <c r="P199" s="7">
+        <v>4.8325985294117642</v>
+      </c>
+      <c r="Q199" s="8">
+        <v>26.77375</v>
+      </c>
+      <c r="R199" s="8">
+        <v>14.882479487179486</v>
+      </c>
+      <c r="S199" s="8">
+        <v>7</v>
+      </c>
+      <c r="T199" s="9">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="U199" s="9">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="V199" s="9">
+        <v>0</v>
+      </c>
+      <c r="W199" s="9">
+        <v>0</v>
+      </c>
+      <c r="X199" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Y199" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="Z199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA199" s="9">
+        <v>0.074999999999999997</v>
+      </c>
+      <c r="AB199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD199" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH199" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI199" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK199" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN199" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AO199" s="6">
+        <v>4</v>
+      </c>
       <c t="s" r="AP199" s="4">
         <v>58</v>
       </c>
@@ -29328,7 +31330,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>51</v>
@@ -29358,35 +31360,93 @@
         <v>58</v>
       </c>
       <c r="L200" s="4"/>
-      <c r="M200" s="5"/>
-      <c r="N200" s="6"/>
-      <c r="O200" s="6"/>
-      <c r="P200" s="7"/>
-      <c r="Q200" s="8"/>
-      <c r="R200" s="8"/>
-      <c r="S200" s="8"/>
-      <c r="T200" s="9"/>
-      <c r="U200" s="9"/>
-      <c r="V200" s="9"/>
-      <c r="W200" s="9"/>
-      <c r="X200" s="9"/>
-      <c r="Y200" s="9"/>
-      <c r="Z200" s="9"/>
-      <c r="AA200" s="9"/>
-      <c r="AB200" s="9"/>
-      <c r="AC200" s="9"/>
-      <c r="AD200" s="6"/>
-      <c r="AE200" s="6"/>
-      <c r="AF200" s="6"/>
-      <c r="AG200" s="6"/>
-      <c r="AH200" s="6"/>
-      <c r="AI200" s="6"/>
-      <c r="AJ200" s="6"/>
-      <c r="AK200" s="6"/>
-      <c r="AL200" s="6"/>
-      <c r="AM200" s="6"/>
-      <c r="AN200" s="9"/>
-      <c r="AO200" s="6"/>
+      <c r="M200" s="5">
+        <v>3722.77</v>
+      </c>
+      <c r="N200" s="6">
+        <v>48</v>
+      </c>
+      <c r="O200" s="6">
+        <v>23</v>
+      </c>
+      <c r="P200" s="7">
+        <v>10.117000000000001</v>
+      </c>
+      <c r="Q200" s="8">
+        <v>20.412317391304349</v>
+      </c>
+      <c r="R200" s="8">
+        <v>4.078335</v>
+      </c>
+      <c r="S200" s="8">
+        <v>7</v>
+      </c>
+      <c r="T200" s="9">
+        <v>0.2608695652173913</v>
+      </c>
+      <c r="U200" s="9">
+        <v>0.13043478260869565</v>
+      </c>
+      <c r="V200" s="9">
+        <v>0</v>
+      </c>
+      <c r="W200" s="9">
+        <v>0</v>
+      </c>
+      <c r="X200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="9">
+        <v>0.13043478260869565</v>
+      </c>
+      <c r="AB200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD200" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK200" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO200" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP200" s="4">
         <v>58</v>
       </c>
@@ -29683,7 +31743,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>51</v>
@@ -29939,7 +31999,7 @@
         <v>19959</v>
       </c>
       <c r="B205" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C205" s="4">
         <v>51</v>
@@ -29969,35 +32029,93 @@
         <v>58</v>
       </c>
       <c r="L205" s="4"/>
-      <c r="M205" s="5"/>
-      <c r="N205" s="6"/>
-      <c r="O205" s="6"/>
-      <c r="P205" s="7"/>
-      <c r="Q205" s="8"/>
-      <c r="R205" s="8"/>
-      <c r="S205" s="8"/>
-      <c r="T205" s="9"/>
-      <c r="U205" s="9"/>
-      <c r="V205" s="9"/>
-      <c r="W205" s="9"/>
-      <c r="X205" s="9"/>
-      <c r="Y205" s="9"/>
-      <c r="Z205" s="9"/>
-      <c r="AA205" s="9"/>
-      <c r="AB205" s="9"/>
-      <c r="AC205" s="9"/>
-      <c r="AD205" s="6"/>
-      <c r="AE205" s="6"/>
-      <c r="AF205" s="6"/>
-      <c r="AG205" s="6"/>
-      <c r="AH205" s="6"/>
-      <c r="AI205" s="6"/>
-      <c r="AJ205" s="6"/>
-      <c r="AK205" s="6"/>
-      <c r="AL205" s="6"/>
-      <c r="AM205" s="6"/>
-      <c r="AN205" s="9"/>
-      <c r="AO205" s="6"/>
+      <c r="M205" s="5">
+        <v>6184.9399999999996</v>
+      </c>
+      <c r="N205" s="6">
+        <v>82</v>
+      </c>
+      <c r="O205" s="6">
+        <v>26</v>
+      </c>
+      <c r="P205" s="7">
+        <v>9.8170837500000001</v>
+      </c>
+      <c r="Q205" s="8">
+        <v>23.008973076923077</v>
+      </c>
+      <c r="R205" s="8">
+        <v>7.5076923076923077</v>
+      </c>
+      <c r="S205" s="8">
+        <v>7</v>
+      </c>
+      <c r="T205" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="U205" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="V205" s="9">
+        <v>0</v>
+      </c>
+      <c r="W205" s="9">
+        <v>0</v>
+      </c>
+      <c r="X205" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="Y205" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA205" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AB205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC205" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="AD205" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE205" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH205" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK205" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM205" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO205" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP205" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-17).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-17).xlsx
@@ -938,34 +938,34 @@
     <t>215</t>
   </si>
   <si>
-    <t>30</t>
+    <t>23</t>
   </si>
   <si>
-    <t>R$ 9.347,25</t>
+    <t>R$ 9.317,03</t>
   </si>
   <si>
-    <t>97.8</t>
+    <t>96.8</t>
   </si>
   <si>
-    <t>62.9</t>
+    <t>63.0</t>
   </si>
   <si>
-    <t>5.94</t>
+    <t>6.01</t>
   </si>
   <si>
     <t>20.2</t>
   </si>
   <si>
-    <t>7.4</t>
+    <t>7.3</t>
   </si>
   <si>
-    <t>6.2</t>
+    <t>6.4</t>
   </si>
   <si>
-    <t>35.4%</t>
+    <t>35.1%</t>
   </si>
   <si>
-    <t>16.6%</t>
+    <t>16.1%</t>
   </si>
   <si>
     <t>1.1%</t>
@@ -974,52 +974,52 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>3.5%</t>
+    <t>3.4%</t>
   </si>
   <si>
-    <t>1.0%</t>
+    <t>0.9%</t>
   </si>
   <si>
     <t>0.1%</t>
   </si>
   <si>
-    <t>5.9%</t>
+    <t>5.7%</t>
   </si>
   <si>
-    <t>2.1%</t>
+    <t>2.0%</t>
   </si>
   <si>
-    <t>5.4%</t>
+    <t>5.2%</t>
   </si>
   <si>
-    <t>2277.0</t>
+    <t>2299.0</t>
   </si>
   <si>
-    <t>1931.0</t>
+    <t>1952.0</t>
   </si>
   <si>
-    <t>128.0</t>
+    <t>131.0</t>
   </si>
   <si>
-    <t>39.0</t>
+    <t>40.0</t>
   </si>
   <si>
-    <t>407.0</t>
+    <t>413.0</t>
   </si>
   <si>
     <t>113.0</t>
   </si>
   <si>
-    <t>13.0</t>
+    <t>15.0</t>
   </si>
   <si>
-    <t>684.0</t>
+    <t>690.0</t>
   </si>
   <si>
-    <t>241.0</t>
+    <t>242.0</t>
   </si>
   <si>
-    <t>630.0</t>
+    <t>634.0</t>
   </si>
   <si>
     <t>0.5%</t>
@@ -2212,7 +2212,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2242,35 +2242,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>13752.48</v>
+      </c>
+      <c r="N6" s="6">
+        <v>134</v>
+      </c>
+      <c r="O6" s="6">
+        <v>95</v>
+      </c>
+      <c r="P6" s="7">
+        <v>10.242692307692307</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>20.153545744680851</v>
+      </c>
+      <c r="R6" s="8">
+        <v>2.8046095744680852</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.35106382978723405</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.031578947368421054</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0.010526315789473684</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.010526315789473684</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.010526315789473684</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -9135,7 +9193,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9165,14 +9223,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>0</v>
+      </c>
+      <c r="N51" s="6">
+        <v>9</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>4.3685222222222215</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>31.330000000000002</v>
+      </c>
+      <c r="R51" s="8">
+        <v>19.443339999999999</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -10204,33 +10274,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>99</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.080808080808080815</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.020202020202020204</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0.010101010101000001</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.010101010101010102</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0.010101010101010102</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0.040404040404040407</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -16638,7 +16754,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16668,35 +16784,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>7441.5100000000002</v>
+      </c>
+      <c r="N102" s="6">
+        <v>72</v>
+      </c>
+      <c r="O102" s="6">
+        <v>49</v>
+      </c>
+      <c r="P102" s="7">
+        <v>12.872916666666667</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>29.203061224489797</v>
+      </c>
+      <c r="R102" s="8">
+        <v>9.401020408163264</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -24003,7 +24177,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -24033,35 +24207,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>7620.1400000000003</v>
+      </c>
+      <c r="N151" s="6">
+        <v>74</v>
+      </c>
+      <c r="O151" s="6">
+        <v>58</v>
+      </c>
+      <c r="P151" s="7">
+        <v>9.0317567567567565</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>18.987643103448278</v>
+      </c>
+      <c r="R151" s="8">
+        <v>3.6479526315789474</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.34482758620689657</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0.017241379310344827</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.051724137931034482</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -24885,7 +25117,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -24915,35 +25147,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>6601.1700000000001</v>
+      </c>
+      <c r="N157" s="6">
+        <v>63</v>
+      </c>
+      <c r="O157" s="6">
+        <v>55</v>
+      </c>
+      <c r="P157" s="7">
+        <v>5.1320111111111117</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>15.67962962962963</v>
+      </c>
+      <c r="R157" s="8">
+        <v>3.6433962264150943</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0.018181818181818181</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0.054545454545454543</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0.018181818181818181</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0.018181818181818181</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -24984,7 +25274,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25014,35 +25304,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>7301.3199999999997</v>
+      </c>
+      <c r="N158" s="6">
+        <v>71</v>
+      </c>
+      <c r="O158" s="6">
+        <v>60</v>
+      </c>
+      <c r="P158" s="7">
+        <v>6.6390471428571427</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>18.771111666666666</v>
+      </c>
+      <c r="R158" s="8">
+        <v>5.0125000000000002</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.23333333333333334</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0.016666666666666666</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0.016666666666666666</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -26019,7 +26367,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26049,35 +26397,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>7625.3599999999997</v>
+      </c>
+      <c r="N165" s="6">
+        <v>71</v>
+      </c>
+      <c r="O165" s="6">
+        <v>45</v>
+      </c>
+      <c r="P165" s="7">
+        <v>6.1997647887323941</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>14.575184444444444</v>
+      </c>
+      <c r="R165" s="8">
+        <v>1.7685177777777776</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>0.64444444444444449</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
